--- a/Дело3а-78-2026Таганай/14_Займы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/14_Займы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.3720483097</v>
+        <v>46158.37400639985</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
